--- a/WBS_OS_Study.xlsx
+++ b/WBS_OS_Study.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2주</t>
+          <t>5일</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2주</t>
+          <t>5일</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3주</t>
+          <t>7일</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4주</t>
+          <t>7일</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3주</t>
+          <t>5일</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1주</t>
+          <t>2일</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3주</t>
+          <t>7일</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2주</t>
+          <t>5일</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1주</t>
+          <t>1일</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1주</t>
+          <t>1일</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4주</t>
+          <t>7일</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2주</t>
+          <t>3일</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1주</t>
+          <t>0.5일</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2주</t>
+          <t>5일</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1주</t>
+          <t>2일</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3주</t>
+          <t>7일</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4주</t>
+          <t>7일</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3주</t>
+          <t>5일</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1주</t>
+          <t>2일</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4주</t>
+          <t>7일</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3주</t>
+          <t>5일</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1주</t>
+          <t>1일</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1주</t>
+          <t>1일</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4주</t>
+          <t>7일</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2주</t>
+          <t>3일</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1주</t>
+          <t>0.5일</t>
         </is>
       </c>
     </row>

--- a/WBS_OS_Study.xlsx
+++ b/WBS_OS_Study.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -510,12 +510,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>C/C++ 기초 문법 학습</t>
+          <t>C 기초 문법 학습</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>5일</t>
+          <t>3일</t>
         </is>
       </c>
     </row>
@@ -527,12 +527,12 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Win32 API 기본 개념 학습</t>
+          <t>C++ 기초 문법 학습</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>5일</t>
+          <t>4일</t>
         </is>
       </c>
     </row>
@@ -544,12 +544,12 @@
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Windows 시스템 프로그래밍 실습</t>
+          <t>Win32 API 개요 파악</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7일</t>
+          <t>1일</t>
         </is>
       </c>
     </row>
@@ -558,19 +558,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Windows OS 관련 서적 찾고 공부하기</t>
-        </is>
-      </c>
+      <c r="C5" s="5" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>'Windows Internals' 서적 정독</t>
+          <t>Win32 API 핵심 함수 실습</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7일</t>
+          <t>3일</t>
         </is>
       </c>
     </row>
@@ -582,12 +578,12 @@
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>'Windows System Programming' 서적 학습</t>
+          <t>Windows 메모리 관리 학습</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5일</t>
+          <t>2일</t>
         </is>
       </c>
     </row>
@@ -599,12 +595,12 @@
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>학습 내용 정리 및 노트 작성</t>
+          <t>Windows 프로세스/스레드 프로그래밍</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2일</t>
+          <t>5일</t>
         </is>
       </c>
     </row>
@@ -613,19 +609,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="n"/>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Windows OS 오픈소스 분석하기</t>
-        </is>
-      </c>
+      <c r="C8" s="5" t="n"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>ReactOS 소스코드 구조 분석</t>
+          <t>Windows 파일 시스템 및 I/O 실습</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7일</t>
+          <t>3일</t>
         </is>
       </c>
     </row>
@@ -637,7 +629,7 @@
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Windows 관련 오픈소스 도구 분석 (Sysinternals 등)</t>
+          <t>Windows 네트워크 프로그래밍 실습</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -651,15 +643,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Windows OS 관련 서적 찾고 공부하기</t>
+        </is>
+      </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>분석 결과 문서화</t>
+          <t>관련 서적 목록 조사 및 선정</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>0.5일</t>
         </is>
       </c>
     </row>
@@ -668,19 +664,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="n"/>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Windows OS 와 관련된 토이프로젝트 하기</t>
-        </is>
-      </c>
+      <c r="C11" s="5" t="n"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>프로젝트 주제 선정 및 설계</t>
+          <t>'Windows Internals Part 1' 정독</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>7일</t>
         </is>
       </c>
     </row>
@@ -692,7 +684,7 @@
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>핵심 기능 구현</t>
+          <t>'Windows Internals Part 2' 정독</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -709,12 +701,12 @@
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>테스트 및 디버깅</t>
+          <t>'Windows System Programming' 서적 학습</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3일</t>
+          <t>5일</t>
         </is>
       </c>
     </row>
@@ -726,12 +718,12 @@
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>프로젝트 문서화 및 회고</t>
+          <t>핵심 내용 요약 노트 작성</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0.5일</t>
+          <t>1일</t>
         </is>
       </c>
     </row>
@@ -739,24 +731,16 @@
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>2. Linux OS</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Linux OS 관련 언어 공부하기</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>C 언어 및 POSIX API 학습</t>
+          <t>학습 내용 블로그/문서 정리</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5일</t>
+          <t>1일</t>
         </is>
       </c>
     </row>
@@ -764,16 +748,20 @@
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Windows OS 오픈소스 분석하기</t>
+        </is>
+      </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Shell Script 작성법 학습</t>
+          <t>분석 대상 오픈소스 프로젝트 선정</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2일</t>
+          <t>0.5일</t>
         </is>
       </c>
     </row>
@@ -781,16 +769,16 @@
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="n"/>
+      <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Linux 시스템 프로그래밍 실습</t>
+          <t>ReactOS 프로젝트 구조 파악</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7일</t>
+          <t>2일</t>
         </is>
       </c>
     </row>
@@ -798,15 +786,11 @@
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Linux OS 관련 서적 찾고 공부하기</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>'Linux Kernel Development' 서적 정독</t>
+          <t>ReactOS 핵심 모듈 소스코드 분석</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -819,16 +803,16 @@
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>'The Linux Programming Interface' 서적 학습</t>
+          <t>Sysinternals 도구 사용법 학습</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5일</t>
+          <t>1일</t>
         </is>
       </c>
     </row>
@@ -836,16 +820,16 @@
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="n"/>
+      <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>학습 내용 정리 및 노트 작성</t>
+          <t>Sysinternals 소스코드 분석</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2일</t>
+          <t>5일</t>
         </is>
       </c>
     </row>
@@ -853,20 +837,16 @@
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Linux OS 오픈소스 분석하기</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Linux Kernel 소스코드 구조 분석</t>
+          <t>분석 결과 문서화</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7일</t>
+          <t>1일</t>
         </is>
       </c>
     </row>
@@ -874,16 +854,20 @@
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Windows OS 와 관련된 토이프로젝트 하기</t>
+        </is>
+      </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>주요 오픈소스 프로젝트 분석 (systemd, busybox 등)</t>
+          <t>프로젝트 아이디어 브레인스토밍</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5일</t>
+          <t>0.5일</t>
         </is>
       </c>
     </row>
@@ -891,16 +875,16 @@
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="n"/>
+      <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="n"/>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>분석 결과 문서화</t>
+          <t>프로젝트 요구사항 정의</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>0.5일</t>
         </is>
       </c>
     </row>
@@ -908,15 +892,11 @@
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Linux OS 와 관련된 토이프로젝트 하기</t>
-        </is>
-      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>프로젝트 주제 선정 및 설계</t>
+          <t>프로젝트 설계 (아키텍처)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -929,16 +909,16 @@
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="n"/>
+      <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>핵심 기능 구현</t>
+          <t>개발 환경 세팅</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7일</t>
+          <t>0.5일</t>
         </is>
       </c>
     </row>
@@ -946,16 +926,16 @@
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="7" t="n"/>
+      <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>테스트 및 디버깅</t>
+          <t>핵심 기능 구현</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3일</t>
+          <t>7일</t>
         </is>
       </c>
     </row>
@@ -963,14 +943,612 @@
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="7" t="n"/>
+      <c r="B27" s="5" t="n"/>
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>프로젝트 문서화 및 회고</t>
+          <t>부가 기능 구현</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>4일</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="25" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>단위 테스트 작성 및 실행</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2일</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="25" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>통합 테스트 및 디버깅</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="25" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>README 및 프로젝트 문서 작성</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0.5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="25" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>코드 리뷰 및 회고</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>0.5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="25" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>2. Linux OS</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Linux OS 관련 언어 공부하기</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>C 언어 복습 및 심화 학습</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="25" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>POSIX API 개요 파악</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="25" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>POSIX API 핵심 함수 실습</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="25" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Shell Script 기본 문법 학습</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="25" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Shell Script 실전 스크립트 작성</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2일</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="25" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Linux 프로세스/스레드 프로그래밍</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="25" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Linux 파일 시스템 및 I/O 실습</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="25" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Linux 소켓 프로그래밍 실습</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="25" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Linux OS 관련 서적 찾고 공부하기</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>관련 서적 목록 조사 및 선정</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>0.5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="25" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>'Linux Kernel Development' 정독</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>7일</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="25" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>'The Linux Programming Interface' 정독</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>7일</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="25" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>'Linux Command Line' 서적 학습</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="25" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>핵심 내용 요약 노트 작성</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="25" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>학습 내용 블로그/문서 정리</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="25" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Linux OS 오픈소스 분석하기</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>분석 대상 오픈소스 프로젝트 선정</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0.5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="25" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Linux Kernel 전체 구조 파악</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>2일</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="25" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Linux Kernel 핵심 서브시스템 분석</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>7일</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="25" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>systemd 소스코드 분석</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="25" customHeight="1">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>busybox 소스코드 분석</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>4일</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="25" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>분석 결과 문서화</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="25" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Linux OS 와 관련된 토이프로젝트 하기</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>프로젝트 아이디어 브레인스토밍</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>0.5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="25" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>프로젝트 요구사항 정의</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>0.5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="25" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>프로젝트 설계 (아키텍처)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="25" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>개발 환경 세팅</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>0.5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="25" customHeight="1">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>핵심 기능 구현</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>7일</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="25" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>부가 기능 구현</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>4일</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="25" customHeight="1">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>단위 테스트 작성 및 실행</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>2일</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="25" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>통합 테스트 및 디버깅</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="25" customHeight="1">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>README 및 프로젝트 문서 작성</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>0.5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="25" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>코드 리뷰 및 회고</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>0.5일</t>
         </is>
@@ -978,16 +1556,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="B15:B27"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="B2:B14"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C46:C51"/>
+    <mergeCell ref="C52:C61"/>
+    <mergeCell ref="C2:C9"/>
+    <mergeCell ref="C32:C39"/>
+    <mergeCell ref="C10:C15"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C40:C45"/>
+    <mergeCell ref="C22:C31"/>
+    <mergeCell ref="B2:B31"/>
+    <mergeCell ref="B32:B61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
